--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487540_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487540_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>C. NOGUEROL BARRENECHEA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.435499999999999</v>
+        <v>9.6149</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8507</v>
+        <v>8.743399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5848</v>
+        <v>0.8714</v>
       </c>
       <c r="G2" t="n">
-        <v>8.256399999999999</v>
+        <v>10.1585</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3158</v>
+        <v>6.1266</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9407</v>
+        <v>4.0319</v>
       </c>
       <c r="J2" t="n">
-        <v>8.2201</v>
+        <v>9.716900000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3106</v>
+        <v>6.3933</v>
       </c>
       <c r="L2" t="n">
-        <v>4.9095</v>
+        <v>3.3237</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0363</v>
+        <v>0.4415</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0052</v>
+        <v>-0.2667</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0311</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R2" t="n">
-        <v>2.1543</v>
+        <v>2.9377</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2794</v>
+        <v>-0.9145</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6099</v>
+        <v>-0.507</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3305</v>
+        <v>-0.4076</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2754</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. NOGUEROL BARRENECHEA</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.2485</v>
+        <v>8.8809</v>
       </c>
       <c r="E3" t="n">
-        <v>8.377000000000001</v>
+        <v>7.2961</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8714</v>
+        <v>1.5848</v>
       </c>
       <c r="G3" t="n">
-        <v>10.1585</v>
+        <v>8.256399999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>6.1266</v>
+        <v>3.3158</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0319</v>
+        <v>4.9407</v>
       </c>
       <c r="J3" t="n">
-        <v>9.716900000000001</v>
+        <v>8.2201</v>
       </c>
       <c r="K3" t="n">
-        <v>6.3933</v>
+        <v>3.3106</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3237</v>
+        <v>4.9095</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4415</v>
+        <v>0.0363</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2667</v>
+        <v>0.0052</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.0311</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9377</v>
+        <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.281</v>
+        <v>-0.2752</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8734</v>
+        <v>0.0553</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4076</v>
+        <v>-0.3305</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6083</v>
+        <v>-0.2754</v>
       </c>
       <c r="W3" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1003</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.49</v>
+        <v>7.2366</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4339</v>
+        <v>4.8597</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0561</v>
+        <v>2.3769</v>
       </c>
       <c r="G4" t="n">
         <v>7.1128</v>
@@ -766,13 +766,13 @@
         <v>2.9377</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8393</v>
+        <v>-1.0928</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0516</v>
+        <v>-0.6258</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7877</v>
+        <v>-0.467</v>
       </c>
       <c r="V4" t="n">
         <v>1.2166</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.744</v>
+        <v>3.4918</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0786</v>
+        <v>2.9333</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6654</v>
+        <v>0.5585</v>
       </c>
       <c r="G5" t="n">
         <v>1.4412</v>
@@ -844,13 +844,13 @@
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3028</v>
+        <v>0.0506</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5634</v>
+        <v>0.4182</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2607</v>
+        <v>-0.3676</v>
       </c>
       <c r="V5" t="n">
         <v>1.2166</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1954</v>
+        <v>3.1303</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9325</v>
+        <v>3.7872</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7371</v>
+        <v>-0.6569</v>
       </c>
       <c r="G6" t="n">
         <v>1.2197</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.083</v>
+        <v>-0.1481</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2247</v>
+        <v>0.0794</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3076</v>
+        <v>-0.2275</v>
       </c>
       <c r="V6" t="n">
         <v>0.8837</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8129</v>
+        <v>1.212</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2306</v>
+        <v>1.6565</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4177</v>
+        <v>-0.4444</v>
       </c>
       <c r="G7" t="n">
         <v>0.6316000000000001</v>
@@ -1000,13 +1000,13 @@
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5813</v>
+        <v>-0.1822</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5346</v>
+        <v>-0.1088</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0466</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1326</v>
+        <v>0.2455</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2283</v>
+        <v>0.2877</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0956</v>
+        <v>-0.0422</v>
       </c>
       <c r="G8" t="n">
         <v>0.2158</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0832</v>
+        <v>0.0297</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>-0.0594</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.094</v>
+        <v>-1.4172</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5706</v>
+        <v>-2.9206</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4767</v>
+        <v>1.5034</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8983</v>
@@ -1156,13 +1156,13 @@
         <v>1.9585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1957</v>
+        <v>-0.5189</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0288</v>
+        <v>-0.3211</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2245</v>
+        <v>-0.1978</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. IGLESIAS GONZALEZ</t>
+          <t>C. MONTERO MECA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3406</v>
+        <v>-2.3788</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8944</v>
+        <v>0.0859</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5538</v>
+        <v>-2.4647</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3585</v>
+        <v>-1.352</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7179</v>
+        <v>-0.8166</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0764</v>
+        <v>-0.5354</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8752</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5018</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3734</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5167</v>
+        <v>-1.352</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2197</v>
+        <v>-0.8166</v>
       </c>
       <c r="O10" t="n">
-        <v>0.703</v>
+        <v>-0.5354</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8962</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1336</v>
+        <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9364</v>
+        <v>-0.006</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8734</v>
+        <v>0.0859</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.063</v>
+        <v>-0.0919</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MONTERO MECA</t>
+          <t>C. IGLESIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6102</v>
+        <v>-2.4078</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1188</v>
+        <v>-4.5874</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4914</v>
+        <v>2.1796</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.352</v>
+        <v>0.3585</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8166</v>
+        <v>-0.7179</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5354</v>
+        <v>1.0764</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.8752</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.5018</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.3734</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.352</v>
+        <v>-0.5167</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8166</v>
+        <v>-1.2197</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5354</v>
+        <v>0.703</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1958</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-4.8962</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1958</v>
+        <v>3.1336</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2374</v>
+        <v>-1.0036</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1188</v>
+        <v>-0.5664</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1186</v>
+        <v>-0.4373</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>27.0141</v>
+        <v>27.6082</v>
       </c>
       <c r="E12" t="n">
-        <v>21.5478</v>
+        <v>22.1418</v>
       </c>
       <c r="F12" t="n">
         <v>5.4664</v>
@@ -1378,7 +1378,7 @@
         <v>-4.0519</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4745999999999997</v>
+        <v>-0.4745999999999996</v>
       </c>
       <c r="P12" t="n">
         <v>3.916900000000001</v>
@@ -1390,13 +1390,13 @@
         <v>16.647</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.6551</v>
+        <v>-4.061</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1438</v>
+        <v>-1.5497</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.5112</v>
+        <v>-2.5115</v>
       </c>
       <c r="V12" t="n">
         <v>0.6083000000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. SANCHEZ CRUZ</t>
+          <t>O. DJAMGOZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9394</v>
+        <v>1.4245</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1341</v>
+        <v>3.0285</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1946</v>
+        <v>-1.604</v>
       </c>
       <c r="G13" t="n">
-        <v>0.981</v>
+        <v>2.0494</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4083</v>
+        <v>-0.5016</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3893</v>
+        <v>2.551</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2529</v>
+        <v>5.7492</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.9254</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2529</v>
+        <v>4.8239</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2719</v>
+        <v>-3.6999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4083</v>
+        <v>-1.427</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1364</v>
+        <v>-2.2729</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0416</v>
+        <v>0.5502</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1188</v>
+        <v>0.217</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0772</v>
+        <v>0.3332</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. DJAMGOZ</t>
+          <t>J. ALIK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9275</v>
+        <v>1.096</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7215</v>
+        <v>1.903</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7939</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0494</v>
+        <v>1.0801</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5016</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2.551</v>
+        <v>0.4194</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7492</v>
+        <v>1.6176</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9254</v>
+        <v>1.6128</v>
       </c>
       <c r="L14" t="n">
-        <v>4.8239</v>
+        <v>0.0048</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.6999</v>
+        <v>-0.5375</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.427</v>
+        <v>-0.952</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.2729</v>
+        <v>0.4145</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7626</v>
+        <v>0.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0533</v>
+        <v>-0.0429</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1433</v>
+        <v>-0.0529</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ALIK</t>
+          <t>S. SANCHEZ CRUZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7889</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>1.596</v>
+        <v>1.1341</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.1679</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0801</v>
+        <v>0.981</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6608000000000001</v>
+        <v>-0.4083</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4194</v>
+        <v>1.3893</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6176</v>
+        <v>1.2529</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6128</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0048</v>
+        <v>1.2529</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5375</v>
+        <v>-0.2719</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.952</v>
+        <v>-0.4083</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4145</v>
+        <v>0.1364</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3499</v>
+        <v>-0.0149</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.297</v>
+        <v>-0.1188</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0529</v>
+        <v>0.104</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0676</v>
+        <v>-1.0785</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0678</v>
+        <v>-0.7608</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003</v>
+        <v>-0.3177</v>
       </c>
       <c r="G16" t="n">
         <v>-2.4035</v>
@@ -1702,13 +1702,13 @@
         <v>1.9585</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0986</v>
+        <v>1.0876</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0306</v>
+        <v>0.2764</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1292</v>
+        <v>0.8112</v>
       </c>
       <c r="V16" t="n">
         <v>1.2166</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.585</v>
+        <v>-2.6094</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2503</v>
+        <v>-1.2847</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8353</v>
+        <v>-1.3247</v>
       </c>
       <c r="G17" t="n">
         <v>-1.9321</v>
@@ -1780,13 +1780,13 @@
         <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6604</v>
+        <v>0.6361</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0338</v>
+        <v>0.4987</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3733</v>
+        <v>0.1373</v>
       </c>
       <c r="V17" t="n">
         <v>0.0576</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1271</v>
+        <v>-2.869</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2459</v>
+        <v>-1.0412</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8812</v>
+        <v>-1.8278</v>
       </c>
       <c r="G18" t="n">
         <v>-3.5158</v>
@@ -1858,13 +1858,13 @@
         <v>0.1958</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4155</v>
+        <v>-0.1573</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2376</v>
+        <v>-0.0329</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1779</v>
+        <v>-0.1244</v>
       </c>
       <c r="V18" t="n">
         <v>0.6083</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3799</v>
+        <v>-3.6243</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.947</v>
+        <v>-1.4587</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4329</v>
+        <v>-2.1656</v>
       </c>
       <c r="G19" t="n">
         <v>-5.0461</v>
@@ -1936,13 +1936,13 @@
         <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2745</v>
+        <v>1.0301</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2327</v>
+        <v>0.721</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0418</v>
+        <v>0.3091</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.1468</v>
+        <v>-5.6898</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8232</v>
+        <v>-2.2326</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.3236</v>
+        <v>-3.4573</v>
       </c>
       <c r="G20" t="n">
         <v>-7.1601</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3877</v>
+        <v>0.8447</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9357</v>
+        <v>0.5264</v>
       </c>
       <c r="U20" t="n">
-        <v>0.452</v>
+        <v>0.3183</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9412</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.6936</v>
+        <v>-5.7163</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8128</v>
+        <v>-2.8917</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8809</v>
+        <v>-2.8246</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9729</v>
@@ -2092,13 +2092,13 @@
         <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.8821</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.607</v>
+        <v>0.3141</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5117</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.6701</v>
+        <v>-8.231199999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2717</v>
+        <v>-1.8624</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.3984</v>
+        <v>-6.3689</v>
       </c>
       <c r="G22" t="n">
         <v>-7.2241</v>
@@ -2170,13 +2170,13 @@
         <v>1.3709</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0828</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.31</v>
+        <v>0.0994</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3928</v>
+        <v>0.4223</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9412</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-27.0143</v>
+        <v>-26.3318</v>
       </c>
       <c r="E23" t="n">
         <v>-5.4665</v>
       </c>
       <c r="F23" t="n">
-        <v>-21.5475</v>
+        <v>-20.8655</v>
       </c>
       <c r="G23" t="n">
         <v>-27.1441</v>
@@ -2248,13 +2248,13 @@
         <v>12.73</v>
       </c>
       <c r="S23" t="n">
-        <v>4.655099999999999</v>
+        <v>5.337400000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5112</v>
+        <v>2.5113</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1439</v>
+        <v>2.8261</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6082000000000002</v>
